--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -67,7 +67,7 @@
     <t>failed</t>
   </si>
   <si>
-    <t>2026-06-19T00:46:24.053Z</t>
+    <t>2026-06-19T22:47:16.433Z</t>
   </si>
   <si>
     <t>https://www.panerabread.com/en-us/home.html</t>
@@ -88,7 +88,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-19T00:48:11.635Z</t>
+    <t>2026-06-19T22:48:09.492Z</t>
   </si>
   <si>
     <t>Home | Panera Bread</t>
